--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/scorecard_consolidated_notes.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/scorecard_consolidated_notes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">docket</t>
   </si>
@@ -44,10 +44,7 @@
     <t xml:space="preserve">major_case</t>
   </si>
   <si>
-    <t xml:space="preserve">precedent_alteration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">declareUnconstitutional</t>
+    <t xml:space="preserve">issue</t>
   </si>
   <si>
     <t xml:space="preserve">25-406</t>
@@ -56,7 +53,7 @@
     <t xml:space="preserve">April</t>
   </si>
   <si>
-    <t xml:space="preserve">FCC v. AT&amp;T</t>
+    <t xml:space="preserve">FCC v. AT\&amp;T</t>
   </si>
   <si>
     <t xml:space="preserve">CA5</t>
@@ -75,6 +72,57 @@
   </si>
   <si>
     <t xml:space="preserve">AT\&amp;T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrative Law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-1083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mullin, Sec. of Homeland Security v. Doe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump, President of United States v. MIOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-1084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CADC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mullin v. Doe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immigration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">November</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Resources, Inc. v. Trump, President of U.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump, President of U.S. v. V.O.S. Selections, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAFED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presidential Power</t>
   </si>
 </sst>
 </file>
@@ -437,41 +485,107 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2"/>
+      <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/scorecard_consolidated_notes.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/scorecard_consolidated_notes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t xml:space="preserve">docket</t>
   </si>
@@ -99,6 +99,33 @@
   </si>
   <si>
     <t xml:space="preserve">Immigration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">January</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Virginia v. B.P.J.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Little v. Hecox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.P.J.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender Identity</t>
   </si>
   <si>
     <t xml:space="preserve">24-1287</t>
@@ -563,28 +590,61 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="I5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>36</v>
+      <c r="K5" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/scorecard_consolidated_notes.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/scorecard_consolidated_notes.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Mullin, Sec. of Homeland Security v. Doe</t>
   </si>
   <si>
-    <t xml:space="preserve">Trump, President of United States v. MIOT</t>
+    <t xml:space="preserve">Trump, President of U.S. v. MIOT</t>
   </si>
   <si>
     <t xml:space="preserve">25-1084</t>
